--- a/data/sweetpotato-heading.xlsx
+++ b/data/sweetpotato-heading.xlsx
@@ -1,41 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-protocols/data/sweetpotato/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-protocols/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76DE63C7-D2F5-E542-9D91-1C1DDE8FA6A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98FC594-378E-2E4F-BDBE-63EE9E244F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="16700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="title" sheetId="7" r:id="rId1"/>
-    <sheet name="crop" sheetId="1" r:id="rId2"/>
-    <sheet name="authors" sheetId="2" r:id="rId3"/>
-    <sheet name="roles_options" sheetId="6" r:id="rId4"/>
-    <sheet name="funders" sheetId="3" r:id="rId5"/>
-    <sheet name="communities" sheetId="4" r:id="rId6"/>
+    <sheet name="crop" sheetId="1" r:id="rId1"/>
+    <sheet name="authors" sheetId="2" r:id="rId2"/>
+    <sheet name="roles_options" sheetId="6" r:id="rId3"/>
+    <sheet name="funders" sheetId="3" r:id="rId4"/>
+    <sheet name="communities" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="96">
   <si>
     <t>key</t>
   </si>
   <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>language</t>
-  </si>
-  <si>
     <t>given_name</t>
   </si>
   <si>
@@ -291,40 +284,34 @@
     <t>sweet potato</t>
   </si>
   <si>
+    <t>autority</t>
+  </si>
+  <si>
+    <t>(L.) Lam.</t>
+  </si>
+  <si>
+    <t>pt</t>
+  </si>
+  <si>
+    <t>batata doce</t>
+  </si>
+  <si>
+    <t>fr</t>
+  </si>
+  <si>
+    <t>es</t>
+  </si>
+  <si>
+    <t>sw</t>
+  </si>
+  <si>
+    <t>camote</t>
+  </si>
+  <si>
+    <t>patate douce</t>
+  </si>
+  <si>
     <t>en</t>
-  </si>
-  <si>
-    <t>pt</t>
-  </si>
-  <si>
-    <t>es</t>
-  </si>
-  <si>
-    <t>fr</t>
-  </si>
-  <si>
-    <t>sw</t>
-  </si>
-  <si>
-    <t>autority</t>
-  </si>
-  <si>
-    <t>(L.) Lam.</t>
-  </si>
-  <si>
-    <t>Standard operating procedures for on-farm testing with the tricot approach</t>
-  </si>
-  <si>
-    <t>Procedimentos operacionais padrão para testes em fazendas com a abordagem tricot</t>
-  </si>
-  <si>
-    <t>Procédures opérationnelles standard pour les tests en milieu agricole avec l'approche tricot</t>
-  </si>
-  <si>
-    <t>Procedimientos operativos estándar para pruebas en finca con el método de tricot</t>
-  </si>
-  <si>
-    <t>Taratibu za kawaida za uendeshaji wa majaribio shambani kwa kutumia mbinu ya tricot</t>
   </si>
 </sst>
 </file>
@@ -422,7 +409,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -436,7 +423,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -741,56 +727,83 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C19487-EA8B-3E4D-A9F2-7C0B9280C706}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B6" t="s">
-        <v>96</v>
+        <v>87</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -799,52 +812,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -859,130 +826,130 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" t="s">
         <v>75</v>
-      </c>
-      <c r="B5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E5" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
         <v>28</v>
       </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
       <c r="D6" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
       <c r="D7" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
         <v>9</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
       <c r="D8" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -990,7 +957,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE575FE-0F55-F349-A431-1CE340853AB3}">
   <dimension ref="A1:B1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -1002,178 +969,178 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2160,7 +2127,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2173,30 +2140,30 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -2210,7 +2177,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2220,18 +2187,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/data/sweetpotato-heading.xlsx
+++ b/data/sweetpotato-heading.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-protocols/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98FC594-378E-2E4F-BDBE-63EE9E244F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23B0A1C-71E8-F942-B227-DCE53A0AC610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="16700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="crop" sheetId="1" r:id="rId1"/>
     <sheet name="authors" sheetId="2" r:id="rId2"/>
     <sheet name="roles_options" sheetId="6" r:id="rId3"/>
     <sheet name="funders" sheetId="3" r:id="rId4"/>
-    <sheet name="communities" sheetId="4" r:id="rId5"/>
+    <sheet name="plotsize" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="103">
   <si>
     <t>key</t>
   </si>
@@ -77,12 +77,6 @@
     <t>grant_number</t>
   </si>
   <si>
-    <t>community_id</t>
-  </si>
-  <si>
-    <t>community_name</t>
-  </si>
-  <si>
     <t>Gates Foundation</t>
   </si>
   <si>
@@ -95,12 +89,6 @@
     <t>INV-031561</t>
   </si>
   <si>
-    <t>cropontologycop</t>
-  </si>
-  <si>
-    <t>Crop Ontology Community</t>
-  </si>
-  <si>
     <t>Bioversity International</t>
   </si>
   <si>
@@ -312,13 +300,46 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>entry</t>
+  </si>
+  <si>
+    <t>plotsize</t>
+  </si>
+  <si>
+    <t>numberseeds</t>
+  </si>
+  <si>
+    <t>10 x 10 m</t>
+  </si>
+  <si>
+    <t>200 vinhas</t>
+  </si>
+  <si>
+    <t>200 vines</t>
+  </si>
+  <si>
+    <t>doi</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5281/zenodo.20525269</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5281/zenodo.20525270</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5281/zenodo.20525271</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5281/zenodo.20525272</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -372,6 +393,20 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -405,11 +440,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -423,8 +459,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{A6F6DD11-FDD5-2F4B-878B-3B453426DB06}"/>
   </cellStyles>
@@ -728,11 +766,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -740,73 +779,95 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" t="s">
         <v>88</v>
-      </c>
-      <c r="D1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" t="s">
         <v>85</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" t="s">
         <v>89</v>
-      </c>
-      <c r="D2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E2" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E4" t="s">
-        <v>87</v>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{31FC9E88-015D-1B4C-9200-F8EDF77465F1}"/>
+    <hyperlink ref="C5:E5" r:id="rId2" display="https://doi.org/10.5281/zenodo.20525269" xr:uid="{3BCCBE4E-2A57-E84E-A612-7EB0E1B7C79B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -846,75 +907,75 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F6" s="3"/>
     </row>
@@ -929,10 +990,10 @@
         <v>12</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -946,10 +1007,10 @@
         <v>11</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -969,178 +1030,178 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2154,16 +2215,16 @@
     </row>
     <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -2178,30 +2239,57 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9974D128-F4F6-DA46-9B66-4D1652C61A48}">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>95</v>
+      </c>
+      <c r="C2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/sweetpotato-heading.xlsx
+++ b/data/sweetpotato-heading.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-protocols/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23B0A1C-71E8-F942-B227-DCE53A0AC610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9DE5635-2872-0E4F-99D7-607A77B91949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="113">
   <si>
     <t>key</t>
   </si>
@@ -311,15 +311,6 @@
     <t>numberseeds</t>
   </si>
   <si>
-    <t>10 x 10 m</t>
-  </si>
-  <si>
-    <t>200 vinhas</t>
-  </si>
-  <si>
-    <t>200 vines</t>
-  </si>
-  <si>
     <t>doi</t>
   </si>
   <si>
@@ -333,6 +324,45 @@
   </si>
   <si>
     <t>https://doi.org/10.5281/zenodo.20525272</t>
+  </si>
+  <si>
+    <t>4 lines of 3 m, with 1 m spacing between lines</t>
+  </si>
+  <si>
+    <t>4 linhas de 3 m, com 1 m de espaço entre linhas</t>
+  </si>
+  <si>
+    <t>x vines</t>
+  </si>
+  <si>
+    <t>x vinhas</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5281/zenodo.20525273</t>
+  </si>
+  <si>
+    <t>0000-0003-3695-7827</t>
+  </si>
+  <si>
+    <t>4 rangs de 3 m, avec un espacement de 1 m entre les rangs</t>
+  </si>
+  <si>
+    <t>4 surcos de 3 m, con 1 m de separación entre surcos</t>
+  </si>
+  <si>
+    <t>Mistari 4 yenye urefu wa m 3, na nafasi ya m 1 kati ya mistari</t>
+  </si>
+  <si>
+    <t>x plantas</t>
+  </si>
+  <si>
+    <t>x plantes</t>
+  </si>
+  <si>
+    <t>x mimea</t>
+  </si>
+  <si>
+    <t>kiazi kitamu</t>
   </si>
 </sst>
 </file>
@@ -767,12 +797,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -810,6 +835,9 @@
       <c r="E2" t="s">
         <v>89</v>
       </c>
+      <c r="F2" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -827,6 +855,9 @@
       <c r="E3" t="s">
         <v>80</v>
       </c>
+      <c r="F3" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -844,22 +875,28 @@
       <c r="E4" t="s">
         <v>83</v>
       </c>
+      <c r="F4" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>102</v>
+      <c r="F5" s="9" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -867,6 +904,7 @@
   <hyperlinks>
     <hyperlink ref="B5" r:id="rId1" xr:uid="{31FC9E88-015D-1B4C-9200-F8EDF77465F1}"/>
     <hyperlink ref="C5:E5" r:id="rId2" display="https://doi.org/10.5281/zenodo.20525269" xr:uid="{3BCCBE4E-2A57-E84E-A612-7EB0E1B7C79B}"/>
+    <hyperlink ref="F5" r:id="rId3" display="https://doi.org/10.5281/zenodo.20525269" xr:uid="{58F2D762-C655-D649-945D-3C69C1601649}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -953,6 +991,9 @@
       </c>
       <c r="B5" t="s">
         <v>70</v>
+      </c>
+      <c r="C5" t="s">
+        <v>105</v>
       </c>
       <c r="D5" t="s">
         <v>55</v>
@@ -2244,6 +2285,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -2271,10 +2314,19 @@
         <v>93</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>101</v>
+      </c>
+      <c r="D2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F2" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -2282,10 +2334,19 @@
         <v>94</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>103</v>
+      </c>
+      <c r="D3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F3" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/data/sweetpotato-heading.xlsx
+++ b/data/sweetpotato-heading.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-protocols/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9DE5635-2872-0E4F-99D7-607A77B91949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82DA56C-1A71-CF4F-94F0-97FC4ABCBC75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -290,9 +290,6 @@
     <t>es</t>
   </si>
   <si>
-    <t>sw</t>
-  </si>
-  <si>
     <t>camote</t>
   </si>
   <si>
@@ -363,6 +360,9 @@
   </si>
   <si>
     <t>kiazi kitamu</t>
+  </si>
+  <si>
+    <t>swh</t>
   </si>
 </sst>
 </file>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C1" t="s">
         <v>84</v>
@@ -816,7 +816,7 @@
         <v>87</v>
       </c>
       <c r="F1" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -830,13 +830,13 @@
         <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -881,22 +881,22 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="C5" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>99</v>
-      </c>
       <c r="F5" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -993,7 +993,7 @@
         <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
         <v>55</v>
@@ -2291,10 +2291,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C1" t="s">
         <v>84</v>
@@ -2306,47 +2306,47 @@
         <v>87</v>
       </c>
       <c r="F1" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" t="s">
         <v>100</v>
       </c>
-      <c r="C2" t="s">
-        <v>101</v>
-      </c>
       <c r="D2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" t="s">
         <v>106</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>107</v>
-      </c>
-      <c r="F2" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" t="s">
         <v>102</v>
       </c>
-      <c r="C3" t="s">
-        <v>103</v>
-      </c>
       <c r="D3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3" t="s">
         <v>110</v>
-      </c>
-      <c r="E3" t="s">
-        <v>109</v>
-      </c>
-      <c r="F3" t="s">
-        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/data/sweetpotato-heading.xlsx
+++ b/data/sweetpotato-heading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-protocols/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D82DA56C-1A71-CF4F-94F0-97FC4ABCBC75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D824606-33EE-374D-8516-A7613D8285A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="16960" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="crop" sheetId="1" r:id="rId1"/>
@@ -329,12 +329,6 @@
     <t>4 linhas de 3 m, com 1 m de espaço entre linhas</t>
   </si>
   <si>
-    <t>x vines</t>
-  </si>
-  <si>
-    <t>x vinhas</t>
-  </si>
-  <si>
     <t>https://doi.org/10.5281/zenodo.20525273</t>
   </si>
   <si>
@@ -350,19 +344,25 @@
     <t>Mistari 4 yenye urefu wa m 3, na nafasi ya m 1 kati ya mistari</t>
   </si>
   <si>
-    <t>x plantas</t>
-  </si>
-  <si>
-    <t>x plantes</t>
-  </si>
-  <si>
-    <t>x mimea</t>
-  </si>
-  <si>
     <t>kiazi kitamu</t>
   </si>
   <si>
     <t>swh</t>
+  </si>
+  <si>
+    <t>40 vines</t>
+  </si>
+  <si>
+    <t>40 vinhas</t>
+  </si>
+  <si>
+    <t>40 plantes</t>
+  </si>
+  <si>
+    <t>40 plantas</t>
+  </si>
+  <si>
+    <t>40 mimea</t>
   </si>
 </sst>
 </file>
@@ -816,7 +816,7 @@
         <v>87</v>
       </c>
       <c r="F1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -836,7 +836,7 @@
         <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -896,7 +896,7 @@
         <v>98</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -993,7 +993,7 @@
         <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
         <v>55</v>
@@ -2306,7 +2306,7 @@
         <v>87</v>
       </c>
       <c r="F1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -2320,13 +2320,13 @@
         <v>100</v>
       </c>
       <c r="D2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2" t="s">
         <v>105</v>
-      </c>
-      <c r="E2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F2" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -2334,19 +2334,19 @@
         <v>93</v>
       </c>
       <c r="B3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
